--- a/output/laminas_comunales/comunal_i_peringr_median_a_2024_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2024_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>-1.411764705882346</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>-2.898550724637683</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>3.99467376830891</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>5.013550135501355</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>25.35211267605635</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>1.49253731343284</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>-10.80368906455863</v>
       </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>-14.5408163265306</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -580,9 +551,6 @@
       </c>
       <c r="E10">
         <v>-16.20185922974768</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringr_median_a_2024_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2024_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -423,133 +423,152 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sierra Gorda</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B4">
-        <v>7.81</v>
+        <v>7.88</v>
       </c>
       <c r="C4">
-        <v>7.51</v>
+        <v>7.95</v>
       </c>
       <c r="D4">
-        <v>0.2999999999999998</v>
+        <v>-0.07000000000000028</v>
       </c>
       <c r="E4">
-        <v>3.99467376830891</v>
+        <v>-0.8805031446540879</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Calama</t>
+          <t>Sierra Gorda</t>
         </is>
       </c>
       <c r="B5">
-        <v>7.75</v>
+        <v>7.81</v>
       </c>
       <c r="C5">
-        <v>7.38</v>
+        <v>7.51</v>
       </c>
       <c r="D5">
-        <v>0.3700000000000001</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E5">
-        <v>5.013550135501355</v>
+        <v>3.99467376830891</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>María Elena</t>
+          <t>Calama</t>
         </is>
       </c>
       <c r="B6">
-        <v>7.12</v>
+        <v>7.75</v>
       </c>
       <c r="C6">
-        <v>5.68</v>
+        <v>7.38</v>
       </c>
       <c r="D6">
-        <v>1.44</v>
+        <v>0.3700000000000001</v>
       </c>
       <c r="E6">
-        <v>25.35211267605635</v>
+        <v>5.013550135501355</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mejillones</t>
+          <t>María Elena</t>
         </is>
       </c>
       <c r="B7">
-        <v>6.8</v>
+        <v>7.12</v>
       </c>
       <c r="C7">
-        <v>6.7</v>
+        <v>5.68</v>
       </c>
       <c r="D7">
-        <v>0.09999999999999964</v>
+        <v>1.44</v>
       </c>
       <c r="E7">
-        <v>1.49253731343284</v>
+        <v>25.35211267605635</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Taltal</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="B8">
-        <v>6.77</v>
+        <v>6.8</v>
       </c>
       <c r="C8">
-        <v>7.59</v>
+        <v>6.7</v>
       </c>
       <c r="D8">
-        <v>-0.8200000000000003</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="E8">
-        <v>-10.80368906455863</v>
+        <v>1.49253731343284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
+          <t>Taltal</t>
         </is>
       </c>
       <c r="B9">
-        <v>6.7</v>
+        <v>6.77</v>
       </c>
       <c r="C9">
-        <v>7.84</v>
+        <v>7.59</v>
       </c>
       <c r="D9">
-        <v>-1.14</v>
+        <v>-0.8200000000000003</v>
       </c>
       <c r="E9">
-        <v>-14.5408163265306</v>
+        <v>-10.80368906455863</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>6.7</v>
+      </c>
+      <c r="C10">
+        <v>7.84</v>
+      </c>
+      <c r="D10">
+        <v>-1.14</v>
+      </c>
+      <c r="E10">
+        <v>-14.5408163265306</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Ollagüe</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>6.31</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>7.53</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>-1.220000000000001</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>-16.20185922974768</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_peringr_median_a_2024_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2024_antofagasta.xlsx
@@ -579,7 +579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -588,20 +588,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>8.039999999999999</v>
+          <t>María Elena</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -610,48 +602,33 @@
           <t>Calama</t>
         </is>
       </c>
-      <c r="B3">
-        <v>7.75</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>María Elena</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>7.12</v>
+          <t>Tocopilla</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mejillones</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>6.8</v>
+          <t>Antofagasta</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ollagüe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>6.31</v>
+          <t>Mejillones</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>6.7</v>
+          <t>Taltal</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -660,28 +637,19 @@
           <t>Sierra Gorda</t>
         </is>
       </c>
-      <c r="B8">
-        <v>7.81</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Taltal</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>6.77</v>
+          <t>San Pedro de Atacama</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tocopilla</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>8.380000000000001</v>
+          <t>Ollagüe</t>
+        </is>
       </c>
     </row>
   </sheetData>
